--- a/administrative_forms/032_swimming_pool_maintenance_checklist_form--administrative_forms.xlsx
+++ b/administrative_forms/032_swimming_pool_maintenance_checklist_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'text':_'water_quality'}</t>
+          <t>water_quality</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'text': 'Water Quality'}</t>
+          <t>Water Quality</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'text':_'equipment_function'}</t>
+          <t>equipment_function</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'text': 'Equipment Function'}</t>
+          <t>Equipment Function</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'text':_'pool_chemistry'}</t>
+          <t>pool_chemistry</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'text': 'Pool Chemistry'}</t>
+          <t>Pool Chemistry</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'text':_'pool_circulation'}</t>
+          <t>pool_circulation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'text': 'Pool Circulation'}</t>
+          <t>Pool Circulation</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'text':_'clean_the_pool_floor'}</t>
+          <t>clean_the_pool_floor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'text': 'Clean the pool floor'}</t>
+          <t>Clean the pool floor</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'clean_the_pool_walls'}</t>
+          <t>clean_the_pool_walls</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Clean the pool walls'}</t>
+          <t>Clean the pool walls</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'clean_the_pool_steps'}</t>
+          <t>clean_the_pool_steps</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Clean the pool steps'}</t>
+          <t>Clean the pool steps</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'ph_level'}</t>
+          <t>ph_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'PH Level'}</t>
+          <t>PH Level</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'alkalinity'}</t>
+          <t>alkalinity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'Alkalinity'}</t>
+          <t>Alkalinity</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'stabilizer'}</t>
+          <t>stabilizer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Stabilizer'}</t>
+          <t>Stabilizer</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'adjust_chemical_levels'}</t>
+          <t>adjust_chemical_levels</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Adjust Chemical Levels'}</t>
+          <t>Adjust Chemical Levels</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'check_for_imbalances'}</t>
+          <t>check_for_imbalances</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'Check for Imbalances'}</t>
+          <t>Check for Imbalances</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'test_pumps'}</t>
+          <t>test_pumps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Test Pumps'}</t>
+          <t>Test Pumps</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'test_filters'}</t>
+          <t>test_filters</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Test Filters'}</t>
+          <t>Test Filters</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'test_valves'}</t>
+          <t>test_valves</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'Test Valves'}</t>
+          <t>Test Valves</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'partial'}</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Partial'}</t>
+          <t>Partial</t>
         </is>
       </c>
     </row>
